--- a/agent_result.xlsx
+++ b/agent_result.xlsx
@@ -413,49 +413,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>sale_date</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>total_amount</t>
+          <t>total_sale_amount</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>电脑</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8998</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3198</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>5599</v>
+        <v>11598</v>
       </c>
     </row>
   </sheetData>
